--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260808" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260808" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -510,10 +510,7 @@
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,11 +537,8 @@
       <c r="M3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="4" t="n">
         <v>46241</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>46242</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -625,37 +619,22 @@
           <t>%</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>NEW SALES</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL SOLD</t>
-        </is>
-      </c>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -718,29 +697,18 @@
         <f>N5/$F$5</f>
         <v/>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="12">
         <f>Q5-N5</f>
         <v/>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="R5" s="11">
+      <c r="R5" s="13">
         <f>Q5/$F$5</f>
         <v/>
       </c>
-      <c r="S5" s="12">
-        <f>T5-Q5</f>
-        <v/>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="U5" s="13">
-        <f>T5/$F$5</f>
-        <v/>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -803,29 +771,18 @@
         <f>N6/$F$6</f>
         <v/>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="12">
         <f>Q6-N6</f>
         <v/>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="13">
         <f>Q6/$F$6</f>
         <v/>
       </c>
-      <c r="S6" s="12">
-        <f>T6-Q6</f>
-        <v/>
-      </c>
-      <c r="T6" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="U6" s="13">
-        <f>T6/$F$6</f>
-        <v/>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -888,29 +845,18 @@
         <f>N7/$F$7</f>
         <v/>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="12">
         <f>Q7-N7</f>
         <v/>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="Q7" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="13">
         <f>Q7/$F$7</f>
         <v/>
       </c>
-      <c r="S7" s="12">
-        <f>T7-Q7</f>
-        <v/>
-      </c>
-      <c r="T7" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="U7" s="13">
-        <f>T7/$F$7</f>
-        <v/>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -973,29 +919,18 @@
         <f>N8/$F$8</f>
         <v/>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="12">
         <f>Q8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="13">
         <f>Q8/$F$8</f>
         <v/>
       </c>
-      <c r="S8" s="12">
-        <f>T8-Q8</f>
-        <v/>
-      </c>
-      <c r="T8" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="U8" s="13">
-        <f>T8/$F$8</f>
-        <v/>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1058,29 +993,18 @@
         <f>N9/$F$9</f>
         <v/>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="12">
         <f>Q9-N9</f>
         <v/>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="11">
+      <c r="R9" s="13">
         <f>Q9/$F$9</f>
         <v/>
       </c>
-      <c r="S9" s="12">
-        <f>T9-Q9</f>
-        <v/>
-      </c>
-      <c r="T9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="13">
-        <f>T9/$F$9</f>
-        <v/>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1133,41 +1057,29 @@
         <f>N10/$F$10</f>
         <v/>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="12">
         <f>Q10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="R10" s="11">
+      <c r="R10" s="13">
         <f>Q10/$F$10</f>
         <v/>
       </c>
-      <c r="S10" s="12">
-        <f>T10-Q10</f>
-        <v/>
-      </c>
-      <c r="T10" s="12" t="n">
-        <v>271</v>
-      </c>
-      <c r="U10" s="13">
-        <f>T10/$F$10</f>
-        <v/>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="G3:I3"/>
+  <mergeCells count="4">
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,10 @@
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="42" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,8 +540,11 @@
       <c r="M3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="3" t="n">
         <v>46241</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>46248</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -619,22 +625,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -697,18 +718,29 @@
         <f>N5/$F$5</f>
         <v/>
       </c>
-      <c r="P5" s="12">
+      <c r="P5" s="10">
         <f>Q5-N5</f>
         <v/>
       </c>
-      <c r="Q5" s="12" t="n">
+      <c r="Q5" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="11">
         <f>Q5/$F$5</f>
         <v/>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="S5" s="12">
+        <f>T5-Q5</f>
+        <v/>
+      </c>
+      <c r="T5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="U5" s="13">
+        <f>T5/$F$5</f>
+        <v/>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -771,18 +803,29 @@
         <f>N6/$F$6</f>
         <v/>
       </c>
-      <c r="P6" s="12">
+      <c r="P6" s="10">
         <f>Q6-N6</f>
         <v/>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="11">
         <f>Q6/$F$6</f>
         <v/>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="12">
+        <f>T6-Q6</f>
+        <v/>
+      </c>
+      <c r="T6" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="U6" s="13">
+        <f>T6/$F$6</f>
+        <v/>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -845,18 +888,29 @@
         <f>N7/$F$7</f>
         <v/>
       </c>
-      <c r="P7" s="12">
+      <c r="P7" s="10">
         <f>Q7-N7</f>
         <v/>
       </c>
-      <c r="Q7" s="12" t="n">
+      <c r="Q7" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="11">
         <f>Q7/$F$7</f>
         <v/>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="S7" s="12">
+        <f>T7-Q7</f>
+        <v/>
+      </c>
+      <c r="T7" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="U7" s="13">
+        <f>T7/$F$7</f>
+        <v/>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -919,18 +973,29 @@
         <f>N8/$F$8</f>
         <v/>
       </c>
-      <c r="P8" s="12">
+      <c r="P8" s="10">
         <f>Q8-N8</f>
         <v/>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="11">
         <f>Q8/$F$8</f>
         <v/>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="S8" s="12">
+        <f>T8-Q8</f>
+        <v/>
+      </c>
+      <c r="T8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="U8" s="13">
+        <f>T8/$F$8</f>
+        <v/>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -993,18 +1058,29 @@
         <f>N9/$F$9</f>
         <v/>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="10">
         <f>Q9-N9</f>
         <v/>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="13">
+      <c r="R9" s="11">
         <f>Q9/$F$9</f>
         <v/>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="12">
+        <f>T9-Q9</f>
+        <v/>
+      </c>
+      <c r="T9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="13">
+        <f>T9/$F$9</f>
+        <v/>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1057,29 +1133,41 @@
         <f>N10/$F$10</f>
         <v/>
       </c>
-      <c r="P10" s="12">
+      <c r="P10" s="10">
         <f>Q10-N10</f>
         <v/>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="10" t="n">
         <v>262</v>
       </c>
-      <c r="R10" s="13">
+      <c r="R10" s="11">
         <f>Q10/$F$10</f>
         <v/>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="S10" s="12">
+        <f>T10-Q10</f>
+        <v/>
+      </c>
+      <c r="T10" s="12" t="n">
+        <v>306</v>
+      </c>
+      <c r="U10" s="13">
+        <f>T10/$F$10</f>
+        <v/>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,10 @@
     <col width="9" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="42" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,8 +546,11 @@
       <c r="P3" s="3" t="n">
         <v>46241</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="S3" s="3" t="n">
         <v>46248</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>46255</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -640,22 +646,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -729,18 +750,29 @@
         <f>Q5/$F$5</f>
         <v/>
       </c>
-      <c r="S5" s="12">
+      <c r="S5" s="10">
         <f>T5-Q5</f>
         <v/>
       </c>
-      <c r="T5" s="12" t="n">
+      <c r="T5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="U5" s="13">
+      <c r="U5" s="11">
         <f>T5/$F$5</f>
         <v/>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="V5" s="12">
+        <f>W5-T5</f>
+        <v/>
+      </c>
+      <c r="W5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="X5" s="13">
+        <f>W5/$F$5</f>
+        <v/>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -814,18 +846,29 @@
         <f>Q6/$F$6</f>
         <v/>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="10">
         <f>T6-Q6</f>
         <v/>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="U6" s="13">
+      <c r="U6" s="11">
         <f>T6/$F$6</f>
         <v/>
       </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="V6" s="12">
+        <f>W6-T6</f>
+        <v/>
+      </c>
+      <c r="W6" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="X6" s="13">
+        <f>W6/$F$6</f>
+        <v/>
+      </c>
+      <c r="Y6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -899,18 +942,29 @@
         <f>Q7/$F$7</f>
         <v/>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="10">
         <f>T7-Q7</f>
         <v/>
       </c>
-      <c r="T7" s="12" t="n">
+      <c r="T7" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="U7" s="13">
+      <c r="U7" s="11">
         <f>T7/$F$7</f>
         <v/>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="V7" s="12">
+        <f>W7-T7</f>
+        <v/>
+      </c>
+      <c r="W7" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="X7" s="13">
+        <f>W7/$F$7</f>
+        <v/>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -984,18 +1038,29 @@
         <f>Q8/$F$8</f>
         <v/>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="10">
         <f>T8-Q8</f>
         <v/>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="U8" s="13">
+      <c r="U8" s="11">
         <f>T8/$F$8</f>
         <v/>
       </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="V8" s="12">
+        <f>W8-T8</f>
+        <v/>
+      </c>
+      <c r="W8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="X8" s="13">
+        <f>W8/$F$8</f>
+        <v/>
+      </c>
+      <c r="Y8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1069,18 +1134,29 @@
         <f>Q9/$F$9</f>
         <v/>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="10">
         <f>T9-Q9</f>
         <v/>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="T9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="13">
+      <c r="U9" s="11">
         <f>T9/$F$9</f>
         <v/>
       </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="V9" s="12">
+        <f>W9-T9</f>
+        <v/>
+      </c>
+      <c r="W9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="13">
+        <f>W9/$F$9</f>
+        <v/>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1144,28 +1220,40 @@
         <f>Q10/$F$10</f>
         <v/>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="10">
         <f>T10-Q10</f>
         <v/>
       </c>
-      <c r="T10" s="12" t="n">
+      <c r="T10" s="10" t="n">
         <v>306</v>
       </c>
-      <c r="U10" s="13">
+      <c r="U10" s="11">
         <f>T10/$F$10</f>
         <v/>
       </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="V10" s="12">
+        <f>W10-T10</f>
+        <v/>
+      </c>
+      <c r="W10" s="12" t="n">
+        <v>335</v>
+      </c>
+      <c r="X10" s="13">
+        <f>W10/$F$10</f>
+        <v/>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>
+    <mergeCell ref="V3:X3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
   </mergeCells>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1248,6 +1248,58 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>MAIA</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>30141-2</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>UEM Sunrise (Laser Tower S/B)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n">
+        <v>495</v>
+      </c>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="12" t="n"/>
+      <c r="W11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="13">
+        <f>W11/$F$11</f>
+        <v/>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>Not yet launched</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="M3:O3"/>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,10 @@
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="42" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="42" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,8 +552,11 @@
       <c r="S3" s="3" t="n">
         <v>46248</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="3" t="n">
         <v>46255</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <v>46262</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -661,22 +667,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="W4" s="6" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="X4" s="6" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AA4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -761,18 +782,29 @@
         <f>T5/$F$5</f>
         <v/>
       </c>
-      <c r="V5" s="12">
+      <c r="V5" s="10">
         <f>W5-T5</f>
         <v/>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="X5" s="13">
+      <c r="X5" s="11">
         <f>W5/$F$5</f>
         <v/>
       </c>
-      <c r="Y5" s="8" t="inlineStr">
+      <c r="Y5" s="12">
+        <f>Z5-W5</f>
+        <v/>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA5" s="13">
+        <f>Z5/$F$5</f>
+        <v/>
+      </c>
+      <c r="AB5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -857,18 +889,29 @@
         <f>T6/$F$6</f>
         <v/>
       </c>
-      <c r="V6" s="12">
+      <c r="V6" s="10">
         <f>W6-T6</f>
         <v/>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="X6" s="13">
+      <c r="X6" s="11">
         <f>W6/$F$6</f>
         <v/>
       </c>
-      <c r="Y6" s="8" t="inlineStr">
+      <c r="Y6" s="12">
+        <f>Z6-W6</f>
+        <v/>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA6" s="13">
+        <f>Z6/$F$6</f>
+        <v/>
+      </c>
+      <c r="AB6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -953,18 +996,29 @@
         <f>T7/$F$7</f>
         <v/>
       </c>
-      <c r="V7" s="12">
+      <c r="V7" s="10">
         <f>W7-T7</f>
         <v/>
       </c>
-      <c r="W7" s="12" t="n">
+      <c r="W7" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="X7" s="13">
+      <c r="X7" s="11">
         <f>W7/$F$7</f>
         <v/>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="Y7" s="12">
+        <f>Z7-W7</f>
+        <v/>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA7" s="13">
+        <f>Z7/$F$7</f>
+        <v/>
+      </c>
+      <c r="AB7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1049,18 +1103,29 @@
         <f>T8/$F$8</f>
         <v/>
       </c>
-      <c r="V8" s="12">
+      <c r="V8" s="10">
         <f>W8-T8</f>
         <v/>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="X8" s="13">
+      <c r="X8" s="11">
         <f>W8/$F$8</f>
         <v/>
       </c>
-      <c r="Y8" s="8" t="inlineStr">
+      <c r="Y8" s="12">
+        <f>Z8-W8</f>
+        <v/>
+      </c>
+      <c r="Z8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="13">
+        <f>Z8/$F$8</f>
+        <v/>
+      </c>
+      <c r="AB8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1145,18 +1210,29 @@
         <f>T9/$F$9</f>
         <v/>
       </c>
-      <c r="V9" s="12">
+      <c r="V9" s="10">
         <f>W9-T9</f>
         <v/>
       </c>
-      <c r="W9" s="12" t="n">
+      <c r="W9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="X9" s="13">
+      <c r="X9" s="11">
         <f>W9/$F$9</f>
         <v/>
       </c>
-      <c r="Y9" s="8" t="inlineStr">
+      <c r="Y9" s="12">
+        <f>Z9-W9</f>
+        <v/>
+      </c>
+      <c r="Z9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="13">
+        <f>Z9/$F$9</f>
+        <v/>
+      </c>
+      <c r="AB9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1231,18 +1307,29 @@
         <f>T10/$F$10</f>
         <v/>
       </c>
-      <c r="V10" s="12">
+      <c r="V10" s="10">
         <f>W10-T10</f>
         <v/>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="10" t="n">
         <v>335</v>
       </c>
-      <c r="X10" s="13">
+      <c r="X10" s="11">
         <f>W10/$F$10</f>
         <v/>
       </c>
-      <c r="Y10" s="8" t="inlineStr">
+      <c r="Y10" s="12">
+        <f>Z10-W10</f>
+        <v/>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>346</v>
+      </c>
+      <c r="AA10" s="13">
+        <f>Z10/$F$10</f>
+        <v/>
+      </c>
+      <c r="AB10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1286,22 +1373,34 @@
       <c r="S11" s="10" t="n"/>
       <c r="T11" s="10" t="n"/>
       <c r="U11" s="11" t="n"/>
-      <c r="V11" s="12" t="n"/>
-      <c r="W11" s="12" t="n">
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="X11" s="13">
+      <c r="X11" s="11">
         <f>W11/$F$11</f>
         <v/>
       </c>
-      <c r="Y11" s="8" t="inlineStr">
+      <c r="Y11" s="12">
+        <f>Z11-W11</f>
+        <v/>
+      </c>
+      <c r="Z11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="13">
+        <f>Z11/$F$11</f>
+        <v/>
+      </c>
+      <c r="AB11" s="8" t="inlineStr">
         <is>
           <t>Not yet launched</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -1012,7 +1012,7 @@
         <v/>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA7" s="13">
         <f>Z7/$F$7</f>
@@ -1323,7 +1323,7 @@
         <v/>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AA10" s="13">
         <f>Z10/$F$10</f>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -1395,11 +1395,7 @@
         <f>Z11/$D$11</f>
         <v/>
       </c>
-      <c r="AB11" s="8" t="inlineStr">
-        <is>
-          <t>Not yet launched</t>
-        </is>
-      </c>
+      <c r="AB11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,10 @@
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
-    <col width="42" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="42" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,8 +558,11 @@
       <c r="V3" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Y3" s="3" t="n">
         <v>46262</v>
+      </c>
+      <c r="AB3" s="4" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -683,22 +689,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="Y4" s="6" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="Z4" s="6" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AA4" s="6" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="AB4" s="5" t="inlineStr">
+      <c r="AB4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AC4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AD4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -794,18 +815,29 @@
         <f>W5/$D$5</f>
         <v/>
       </c>
-      <c r="Y5" s="12">
+      <c r="Y5" s="10">
         <f>Z5-W5</f>
         <v/>
       </c>
-      <c r="Z5" s="12" t="n">
+      <c r="Z5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AA5" s="11">
         <f>Z5/$D$5</f>
         <v/>
       </c>
-      <c r="AB5" s="8" t="inlineStr">
+      <c r="AB5" s="12">
+        <f>AC5-Z5</f>
+        <v/>
+      </c>
+      <c r="AC5" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD5" s="13">
+        <f>AC5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AE5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -901,18 +933,29 @@
         <f>W6/$D$6</f>
         <v/>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="10">
         <f>Z6-W6</f>
         <v/>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AA6" s="11">
         <f>Z6/$D$6</f>
         <v/>
       </c>
-      <c r="AB6" s="8" t="inlineStr">
+      <c r="AB6" s="12">
+        <f>AC6-Z6</f>
+        <v/>
+      </c>
+      <c r="AC6" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD6" s="13">
+        <f>AC6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AE6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -1008,18 +1051,29 @@
         <f>W7/$D$7</f>
         <v/>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="10">
         <f>Z7-W7</f>
         <v/>
       </c>
-      <c r="Z7" s="12" t="n">
+      <c r="Z7" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AA7" s="11">
         <f>Z7/$D$7</f>
         <v/>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
+      <c r="AB7" s="12">
+        <f>AC7-Z7</f>
+        <v/>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD7" s="13">
+        <f>AC7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AE7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1115,18 +1169,29 @@
         <f>W8/$D$8</f>
         <v/>
       </c>
-      <c r="Y8" s="12">
+      <c r="Y8" s="10">
         <f>Z8-W8</f>
         <v/>
       </c>
-      <c r="Z8" s="12" t="n">
+      <c r="Z8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AA8" s="11">
         <f>Z8/$D$8</f>
         <v/>
       </c>
-      <c r="AB8" s="8" t="inlineStr">
+      <c r="AB8" s="12">
+        <f>AC8-Z8</f>
+        <v/>
+      </c>
+      <c r="AC8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD8" s="13">
+        <f>AC8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AE8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1222,18 +1287,29 @@
         <f>W9/$D$9</f>
         <v/>
       </c>
-      <c r="Y9" s="12">
+      <c r="Y9" s="10">
         <f>Z9-W9</f>
         <v/>
       </c>
-      <c r="Z9" s="12" t="n">
+      <c r="Z9" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AA9" s="11">
         <f>Z9/$D$9</f>
         <v/>
       </c>
-      <c r="AB9" s="8" t="inlineStr">
+      <c r="AB9" s="12">
+        <f>AC9-Z9</f>
+        <v/>
+      </c>
+      <c r="AC9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="13">
+        <f>AC9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AE9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1319,18 +1395,29 @@
         <f>W10/$D$10</f>
         <v/>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="10">
         <f>Z10-W10</f>
         <v/>
       </c>
-      <c r="Z10" s="12" t="n">
+      <c r="Z10" s="10" t="n">
         <v>349</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AA10" s="11">
         <f>Z10/$D$10</f>
         <v/>
       </c>
-      <c r="AB10" s="8" t="inlineStr">
+      <c r="AB10" s="12">
+        <f>AC10-Z10</f>
+        <v/>
+      </c>
+      <c r="AC10" s="12" t="n">
+        <v>353</v>
+      </c>
+      <c r="AD10" s="13">
+        <f>AC10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AE10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1384,23 +1471,35 @@
         <f>W11/$D$11</f>
         <v/>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="10">
         <f>Z11-W11</f>
         <v/>
       </c>
-      <c r="Z11" s="12" t="n">
+      <c r="Z11" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AA11" s="11">
         <f>Z11/$D$11</f>
         <v/>
       </c>
-      <c r="AB11" s="8" t="inlineStr"/>
+      <c r="AB11" s="12">
+        <f>AC11-Z11</f>
+        <v/>
+      </c>
+      <c r="AC11" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="13">
+        <f>AC11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AE11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
+    <mergeCell ref="AB3:AD3"/>
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="V3:X3"/>

--- a/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
+++ b/docs/downloads/Seputeh_Hills_Teduh_Weekly_Update.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="20260909" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260910" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 09/09/2026</t>
+          <t>Report as at 10/09/2026</t>
         </is>
       </c>
     </row>
